--- a/HK_Swing_Pattern.xlsx
+++ b/HK_Swing_Pattern.xlsx
@@ -3251,7 +3251,7 @@
         <v>6.3</v>
       </c>
       <c r="AD23" s="2" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="AE23" s="2" t="inlineStr"/>
       <c r="AF23" s="2" t="n">

--- a/HK_Swing_Pattern.xlsx
+++ b/HK_Swing_Pattern.xlsx
@@ -19088,7 +19088,7 @@
         <v>4.223</v>
       </c>
       <c r="AO159" s="2" t="n">
-        <v>4.229</v>
+        <v>4.23</v>
       </c>
       <c r="AP159" s="2" t="n">
         <v>4.705</v>
@@ -29803,7 +29803,7 @@
         <v>63.274</v>
       </c>
       <c r="AO252" s="2" t="n">
-        <v>63.359</v>
+        <v>63.36</v>
       </c>
       <c r="AP252" s="2" t="n">
         <v>65.73999999999999</v>
@@ -42401,7 +42401,7 @@
         <v>10.297</v>
       </c>
       <c r="AM364" s="2" t="n">
-        <v>10.605</v>
+        <v>10.604</v>
       </c>
       <c r="AN364" s="2" t="n">
         <v>10.727</v>
@@ -45081,7 +45081,7 @@
         <v>4.751</v>
       </c>
       <c r="AK388" s="2" t="n">
-        <v>4.58</v>
+        <v>4.581</v>
       </c>
       <c r="AL388" s="2" t="n">
         <v>4.702</v>
@@ -54835,7 +54835,7 @@
         <v>72.059</v>
       </c>
       <c r="AP473" s="2" t="n">
-        <v>69.45</v>
+        <v>69.45099999999999</v>
       </c>
       <c r="AQ473" s="2" t="n">
         <v>-0.197</v>
@@ -55782,7 +55782,7 @@
         <v>95.73999999999999</v>
       </c>
       <c r="AO481" s="2" t="n">
-        <v>107.249</v>
+        <v>107.25</v>
       </c>
       <c r="AP481" s="2" t="n">
         <v>117.764</v>

--- a/HK_Swing_Pattern.xlsx
+++ b/HK_Swing_Pattern.xlsx
@@ -17466,7 +17466,7 @@
         <v>48.296</v>
       </c>
       <c r="AO145" s="2" t="n">
-        <v>51.847</v>
+        <v>51.846</v>
       </c>
       <c r="AP145" s="2" t="n">
         <v>60.085</v>
@@ -18972,7 +18972,7 @@
         <v>0.701</v>
       </c>
       <c r="AN158" s="2" t="n">
-        <v>0.713</v>
+        <v>0.714</v>
       </c>
       <c r="AO158" s="2" t="n">
         <v>0.707</v>
@@ -19088,7 +19088,7 @@
         <v>4.223</v>
       </c>
       <c r="AO159" s="2" t="n">
-        <v>4.23</v>
+        <v>4.229</v>
       </c>
       <c r="AP159" s="2" t="n">
         <v>4.705</v>
@@ -29803,7 +29803,7 @@
         <v>63.274</v>
       </c>
       <c r="AO252" s="2" t="n">
-        <v>63.36</v>
+        <v>63.359</v>
       </c>
       <c r="AP252" s="2" t="n">
         <v>65.73999999999999</v>
@@ -45081,7 +45081,7 @@
         <v>4.751</v>
       </c>
       <c r="AK388" s="2" t="n">
-        <v>4.581</v>
+        <v>4.58</v>
       </c>
       <c r="AL388" s="2" t="n">
         <v>4.702</v>
@@ -54664,7 +54664,7 @@
         <v>33.7</v>
       </c>
       <c r="D472" s="2" t="n">
-        <v>40.4</v>
+        <v>41.22</v>
       </c>
       <c r="E472" s="2" t="inlineStr"/>
       <c r="F472" s="2" t="inlineStr"/>
@@ -57190,7 +57190,7 @@
         <v>8.175000000000001</v>
       </c>
       <c r="AO493" s="2" t="n">
-        <v>7.98</v>
+        <v>7.981</v>
       </c>
       <c r="AP493" s="2" t="n">
         <v>8.795</v>

--- a/HK_Swing_Pattern.xlsx
+++ b/HK_Swing_Pattern.xlsx
@@ -2190,7 +2190,9 @@
       </c>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="R14" s="2" t="inlineStr"/>
       <c r="S14" s="2" t="n">
         <v>1</v>
@@ -40664,7 +40666,9 @@
       </c>
       <c r="O350" s="2" t="inlineStr"/>
       <c r="P350" s="2" t="inlineStr"/>
-      <c r="Q350" s="2" t="inlineStr"/>
+      <c r="Q350" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="R350" s="2" t="n">
         <v>1</v>
       </c>
@@ -41110,7 +41114,9 @@
         <v>1</v>
       </c>
       <c r="P354" s="2" t="inlineStr"/>
-      <c r="Q354" s="2" t="inlineStr"/>
+      <c r="Q354" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="R354" s="2" t="inlineStr">
         <is>
           <t>预-1</t>
@@ -62374,14 +62380,14 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SOS (Sign of Strength, Wyckoff): P1前置(位置门前): {C&gt;MA5, C&gt;MA10, MA5&gt;MA10}三项比较至少2项为正(排除股价在短期均线下方/空头排列)。位置门 = A OR B。A: 200日pos&lt;=0.80(200日数据不足回退3个月); B: 近3日 4均线(5/10/15/20)纠缠 max/min-1&lt;5% 且距250日收盘高点回落≥5%(创新高处的平台突破归新高, 不算SOS)。仙股过滤: 信号K线收盘&lt;0.5(本币)不触发。强度: 放量+RS超额+阳线。捕获纠缠平台突破、次新股底部反强</t>
+          <t xml:space="preserve">  SOS (Sign of Strength, Wyckoff): P1前置: {C&gt;MA5, C&gt;MA10, MA5&gt;MA10}三项比较至少2项为正(排除股价在短期均线下方/空头排列)。强度路径: 放量+RS超额+阳线。无位置门(2026-10-02取消: 原A门200日pos&lt;=0.80/B门均线纠缠+距250日高点回落≥5%/门E Stage 1B-2B 全部移除, 高位/新高处的放量突破同样算SOS)。仙股过滤: 信号K线收盘&lt;0.5(本币)不触发</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    阳线path: 中大阳(实体&gt;3% ∨ 收盘较昨收&gt;3%, 覆盖大幅低开高走) + 收盘位于日内上1/3 + 放量(&gt;=2x 20日均量) + 当日涨幅较指数超额&gt;=2%(A股沪深300指数000300.SH/HK恒指HSI.HI/美股标普500指数^GSPC, 均首选jianxin真实指数, ETF兜底; 基准缺失时跳过此门)</t>
+          <t xml:space="preserve">    阳线path: 中大阳(实体&gt;3% ∨ 收盘较昨收&gt;3%, 覆盖大幅低开高走) + 收盘位于日内上1/3 + 放量(&gt;=2x 20日均量; 海外大盘股池放宽至1.5x) + 当日涨幅较指数超额&gt;=2%(A股沪深300指数000300.SH/HK恒指HSI.HI/美股标普500指数^GSPC, 均首选jianxin真实指数, ETF兜底; 基准缺失时跳过此门)</t>
         </is>
       </c>
     </row>

--- a/HK_Swing_Pattern.xlsx
+++ b/HK_Swing_Pattern.xlsx
@@ -50815,14 +50815,10 @@
       <c r="AC438" s="2" t="n">
         <v>108.2</v>
       </c>
-      <c r="AD438" s="2" t="n">
-        <v>53</v>
-      </c>
+      <c r="AD438" s="2" t="inlineStr"/>
       <c r="AE438" s="2" t="inlineStr"/>
       <c r="AF438" s="2" t="inlineStr"/>
-      <c r="AG438" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="AG438" s="2" t="inlineStr"/>
       <c r="AH438" s="2" t="inlineStr"/>
       <c r="AI438" s="2" t="inlineStr">
         <is>

--- a/HK_Swing_Pattern.xlsx
+++ b/HK_Swing_Pattern.xlsx
@@ -13415,7 +13415,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="AD111" s="2" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="AE111" s="2" t="inlineStr"/>
       <c r="AF111" s="2" t="n">

--- a/HK_Swing_Pattern.xlsx
+++ b/HK_Swing_Pattern.xlsx
@@ -2835,7 +2835,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>1B→3·5d ← 1A→1B·8d ← 1B→1A·9d</t>
+          <t>1+→3·5d ← 1→1+·8d ← 1+→1·9d</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr"/>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>1B→1·16d ← 1→1B·18d</t>
+          <t>1+→1·16d ← 1→1+·18d</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr"/>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>1A→1·4d ← 1B→1A·10d ← 1A→1B·11d</t>
+          <t>1+→1·10d ← 1→1+·11d ← 1+→1·15d</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr"/>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>1→4·9d ← 1A→1·14d ← 1→1A·15d</t>
+          <t>1→4·9d ← 1+→1·17d ← 1→1+·18d</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr"/>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>1A→3·16d ← 1B→1A·17d ← 1A→1B·18d</t>
+          <t>1→3·16d ← 1+→1·17d ← 1→1+·18d</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr"/>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>4+→4·1d ← 4→4+·9d ← 1A→4·17d</t>
+          <t>4+→4·1d ← 4→4+·9d ← 1→4·17d</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr"/>
@@ -9417,7 +9417,7 @@
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>1A→1·10d ← 3→1A·14d</t>
+          <t>3→1·14d</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr"/>
@@ -10480,7 +10480,7 @@
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>1A→1·2d ← 4→1A·3d ← 4+→4·6d</t>
+          <t>4→1·3d ← 4+→4·6d ← 4→4+·9d</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr"/>
@@ -13502,11 +13502,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y86" s="2" t="inlineStr">
-        <is>
-          <t>1A→1·7d ← 1→1A·8d</t>
-        </is>
-      </c>
+      <c r="Y86" s="2" t="inlineStr"/>
       <c r="Z86" s="2" t="inlineStr"/>
       <c r="AA86" s="2" t="inlineStr"/>
       <c r="AB86" s="2" t="inlineStr"/>
@@ -13917,7 +13913,7 @@
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>1B→3·11d ← 4→1B·15d</t>
+          <t>1+→3·11d ← 4→1+·15d</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr"/>
@@ -14372,7 +14368,7 @@
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>1→4·1d ← 1A→1·13d ← 3→1A·14d</t>
+          <t>1→4·1d ← 3→1·14d ← 1+→3·17d</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr"/>
@@ -14678,7 +14674,7 @@
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>1B→2C·2d ← 1A→1B·5d ← 1B→1A·10d</t>
+          <t>1+→2C·2d ← 1→1+·5d ← 1+→1·10d</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr"/>
@@ -15401,7 +15397,7 @@
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>1A→4·20d</t>
+          <t>1→4·20d</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr"/>
@@ -15550,7 +15546,7 @@
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>1A→2A·9d ← 1B→1A·13d</t>
+          <t>1→2A·9d ← 1+→1·13d</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -16790,7 +16786,7 @@
       </c>
       <c r="Y108" s="2" t="inlineStr">
         <is>
-          <t>1A→1·6d ← 3→1A·9d ← NA→3·17d</t>
+          <t>3→1·9d ← NA→3·17d</t>
         </is>
       </c>
       <c r="Z108" s="2" t="inlineStr"/>
@@ -19995,7 +19991,7 @@
       </c>
       <c r="Y129" s="2" t="inlineStr">
         <is>
-          <t>1A→1·2d ← 1→1A·4d ← 1A→1·5d</t>
+          <t>1+→1·19d</t>
         </is>
       </c>
       <c r="Z129" s="2" t="inlineStr"/>
@@ -21971,12 +21967,12 @@
       </c>
       <c r="X142" s="2" t="inlineStr">
         <is>
-          <t>1B(预金叉·纠缠)</t>
+          <t>1+(预金叉·纠缠)</t>
         </is>
       </c>
       <c r="Y142" s="2" t="inlineStr">
         <is>
-          <t>1A→1B·3d ← 1→1A·8d ← 2A→1·14d</t>
+          <t>1→1+·3d ← 2A→1·14d ← 2C→2A·17d</t>
         </is>
       </c>
       <c r="Z142" s="2" t="inlineStr"/>
@@ -22131,7 +22127,7 @@
       </c>
       <c r="Y143" s="2" t="inlineStr">
         <is>
-          <t>3→1·6d ← 1→3·11d ← 1A→1·15d</t>
+          <t>3→1·6d ← 1→3·11d</t>
         </is>
       </c>
       <c r="Z143" s="2" t="inlineStr"/>
@@ -24802,12 +24798,12 @@
       </c>
       <c r="X161" s="2" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y161" s="2" t="inlineStr">
         <is>
-          <t>3→1A·1d ← 1A→3·4d ← 1→1A·7d</t>
+          <t>3→1·1d ← 1→3·4d</t>
         </is>
       </c>
       <c r="Z161" s="2" t="inlineStr"/>
@@ -24958,7 +24954,7 @@
       </c>
       <c r="Y162" s="2" t="inlineStr">
         <is>
-          <t>1→4·9d ← 1A→1·14d ← 1B→1A·16d</t>
+          <t>1→4·9d ← 1+→1·16d ← 1→1+·18d</t>
         </is>
       </c>
       <c r="Z162" s="2" t="inlineStr"/>
@@ -27253,7 +27249,7 @@
       </c>
       <c r="Y177" s="2" t="inlineStr">
         <is>
-          <t>1→4·1d ← 1A→1·6d ← 1→1A·7d</t>
+          <t>1→4·1d</t>
         </is>
       </c>
       <c r="Z177" s="2" t="inlineStr"/>
@@ -28032,7 +28028,7 @@
       </c>
       <c r="Y182" s="2" t="inlineStr">
         <is>
-          <t>1→4·5d ← 1A→1·6d ← 1→1A·13d</t>
+          <t>1→4·5d ← 4→1·19d</t>
         </is>
       </c>
       <c r="Z182" s="2" t="inlineStr"/>
@@ -28175,7 +28171,7 @@
       </c>
       <c r="Y183" s="2" t="inlineStr">
         <is>
-          <t>1A→3·6d ← 1→1A·7d ← 3→1·9d</t>
+          <t>1→3·6d ← 3→1·9d ← 2C→3·13d</t>
         </is>
       </c>
       <c r="Z183" s="2" t="inlineStr"/>
@@ -29597,11 +29593,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y193" s="2" t="inlineStr">
-        <is>
-          <t>1A→1·20d</t>
-        </is>
-      </c>
+      <c r="Y193" s="2" t="inlineStr"/>
       <c r="Z193" s="2" t="inlineStr"/>
       <c r="AA193" s="2" t="inlineStr"/>
       <c r="AB193" s="2" t="n">
@@ -32876,14 +32868,10 @@
       </c>
       <c r="X215" s="2" t="inlineStr">
         <is>
-          <t>1A</t>
-        </is>
-      </c>
-      <c r="Y215" s="2" t="inlineStr">
-        <is>
-          <t>1→1A·2d</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y215" s="2" t="inlineStr"/>
       <c r="Z215" s="2" t="inlineStr"/>
       <c r="AA215" s="2" t="inlineStr"/>
       <c r="AB215" s="2" t="inlineStr"/>
@@ -33334,7 +33322,7 @@
       </c>
       <c r="Y218" s="2" t="inlineStr">
         <is>
-          <t>1A→1·1d ← 1→1A·2d ← 1A→1·3d</t>
+          <t>2A→1·5d ← 2C→2A·6d ← 2A→2C·18d</t>
         </is>
       </c>
       <c r="Z218" s="2" t="inlineStr"/>
@@ -35948,7 +35936,7 @@
       </c>
       <c r="Y236" s="2" t="inlineStr">
         <is>
-          <t>1→4·14d ← 1A→1·17d ← 1→1A·18d</t>
+          <t>1→4·14d</t>
         </is>
       </c>
       <c r="Z236" s="2" t="inlineStr"/>
@@ -36223,12 +36211,12 @@
       </c>
       <c r="X238" s="2" t="inlineStr">
         <is>
-          <t>1B(预金叉·纠缠)</t>
+          <t>1+(预金叉·纠缠)</t>
         </is>
       </c>
       <c r="Y238" s="2" t="inlineStr">
         <is>
-          <t>1A→1B·2d ← 1→1A·3d ← 4→1·9d</t>
+          <t>1→1+·2d ← 1+→1·4d ← 1→1+·5d</t>
         </is>
       </c>
       <c r="Z238" s="2" t="inlineStr"/>
@@ -38055,11 +38043,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y251" s="2" t="inlineStr">
-        <is>
-          <t>1A→1·2d ← 1→1A·3d ← 1A→1·5d</t>
-        </is>
-      </c>
+      <c r="Y251" s="2" t="inlineStr"/>
       <c r="Z251" s="2" t="inlineStr"/>
       <c r="AA251" s="2" t="inlineStr"/>
       <c r="AB251" s="2" t="n">
@@ -38356,12 +38340,12 @@
       </c>
       <c r="X253" s="2" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y253" s="2" t="inlineStr">
         <is>
-          <t>1B→1A·1d ← 1A→1B·2d ← 1B→1A·3d</t>
+          <t>1+→1·1d ← 1→1+·2d ← 1+→1·3d</t>
         </is>
       </c>
       <c r="Z253" s="2" t="inlineStr"/>
@@ -39678,7 +39662,7 @@
       </c>
       <c r="Y262" s="2" t="inlineStr">
         <is>
-          <t>4+→4·8d ← 1A→4+·9d ← 1B→1A·10d</t>
+          <t>4+→4·8d ← 1→4+·9d ← 1+→1·10d</t>
         </is>
       </c>
       <c r="Z262" s="2" t="inlineStr"/>
@@ -40131,7 +40115,7 @@
       </c>
       <c r="Y265" s="2" t="inlineStr">
         <is>
-          <t>3→1·1d ← 1A→3·20d</t>
+          <t>3→1·1d ← 1→3·20d</t>
         </is>
       </c>
       <c r="Z265" s="2" t="inlineStr"/>
@@ -40275,12 +40259,12 @@
       </c>
       <c r="X266" s="2" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y266" s="2" t="inlineStr">
         <is>
-          <t>1→1A·2d ← 1A→1·3d ← 1B→1A·4d</t>
+          <t>1+→1·4d ← 1→1+·5d</t>
         </is>
       </c>
       <c r="Z266" s="2" t="inlineStr"/>
@@ -41877,7 +41861,7 @@
       </c>
       <c r="Y277" s="2" t="inlineStr">
         <is>
-          <t>1B→2A·5d ← 1A→1B·11d ← 1B→1A·12d</t>
+          <t>1+→2A·5d ← 1→1+·11d ← 1+→1·12d</t>
         </is>
       </c>
       <c r="Z277" s="2" t="inlineStr">
@@ -43055,7 +43039,7 @@
       </c>
       <c r="Y285" s="2" t="inlineStr">
         <is>
-          <t>1A→1·6d ← 1B→1A·10d ← 1→1B·11d</t>
+          <t>1+→1·10d ← 1→1+·11d ← 1+→1·15d</t>
         </is>
       </c>
       <c r="Z285" s="2" t="inlineStr"/>
@@ -43951,7 +43935,7 @@
       </c>
       <c r="Y291" s="2" t="inlineStr">
         <is>
-          <t>1A→2A·2d ← 1→1A·7d ← 1A→1·10d</t>
+          <t>1→2A·2d</t>
         </is>
       </c>
       <c r="Z291" s="2" t="inlineStr"/>
@@ -44679,12 +44663,12 @@
       </c>
       <c r="X296" s="2" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y296" s="2" t="inlineStr">
         <is>
-          <t>1B→1A·1d ← 1→1B·5d ← 1A→1·6d</t>
+          <t>1+→1·1d ← 1→1+·5d ← 1+→1·7d</t>
         </is>
       </c>
       <c r="Z296" s="2" t="inlineStr"/>
@@ -45587,12 +45571,12 @@
       </c>
       <c r="X302" s="2" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y302" s="2" t="inlineStr">
         <is>
-          <t>1B→1A·1d ← 1A→1B·2d ← 1B→1A·3d</t>
+          <t>1+→1·1d ← 1→1+·2d ← 1+→1·3d</t>
         </is>
       </c>
       <c r="Z302" s="2" t="inlineStr"/>
@@ -46155,12 +46139,12 @@
       </c>
       <c r="X306" s="2" t="inlineStr">
         <is>
-          <t>1B(预金叉·纠缠)</t>
+          <t>1+(预金叉·纠缠)</t>
         </is>
       </c>
       <c r="Y306" s="2" t="inlineStr">
         <is>
-          <t>1A→1B·4d ← 1→1A·5d ← 1A→1·7d</t>
+          <t>1→1+·4d ← 1+→1·16d ← 1→1+·17d</t>
         </is>
       </c>
       <c r="Z306" s="2" t="inlineStr"/>
@@ -48227,12 +48211,12 @@
       </c>
       <c r="X320" s="2" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y320" s="2" t="inlineStr">
         <is>
-          <t>4+→1A·5d ← 4→4+·7d ← 1→4·10d</t>
+          <t>4+→1·5d ← 4→4+·7d ← 1→4·10d</t>
         </is>
       </c>
       <c r="Z320" s="2" t="inlineStr"/>
@@ -48532,7 +48516,7 @@
       </c>
       <c r="Y322" s="2" t="inlineStr">
         <is>
-          <t>1A→1·2d ← 2A→1A·3d ← 1→2A·9d</t>
+          <t>2A→1·3d ← 1→2A·9d ← 1+→1·15d</t>
         </is>
       </c>
       <c r="Z322" s="2" t="inlineStr"/>
@@ -51786,7 +51770,7 @@
       </c>
       <c r="Y344" s="2" t="inlineStr">
         <is>
-          <t>1A→1·1d ← 3→1A·2d ← 1B→3·8d</t>
+          <t>3→1·2d ← 1+→3·8d ← 4→1+·12d</t>
         </is>
       </c>
       <c r="Z344" s="2" t="inlineStr"/>
@@ -52969,7 +52953,7 @@
       </c>
       <c r="X352" s="2" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y352" s="2" t="inlineStr"/>
@@ -53399,7 +53383,7 @@
       </c>
       <c r="Y355" s="2" t="inlineStr">
         <is>
-          <t>1A→1·5d ← 1→1A·6d ← 1A→1·10d</t>
+          <t>3→1·14d</t>
         </is>
       </c>
       <c r="Z355" s="2" t="inlineStr"/>
@@ -56801,12 +56785,12 @@
       </c>
       <c r="X378" s="2" t="inlineStr">
         <is>
-          <t>1B(预金叉·纠缠)</t>
+          <t>1+(预金叉·纠缠)</t>
         </is>
       </c>
       <c r="Y378" s="2" t="inlineStr">
         <is>
-          <t>4→1B·2d</t>
+          <t>4→1+·2d</t>
         </is>
       </c>
       <c r="Z378" s="2" t="inlineStr"/>
@@ -56959,7 +56943,7 @@
       </c>
       <c r="Y379" s="2" t="inlineStr">
         <is>
-          <t>1A→4·11d ← 1→1A·13d ← 1A→1·16d</t>
+          <t>1→4·11d</t>
         </is>
       </c>
       <c r="Z379" s="2" t="inlineStr"/>
@@ -61187,7 +61171,7 @@
       </c>
       <c r="Y407" s="2" t="inlineStr">
         <is>
-          <t>1A→3·8d ← 1→1A·13d</t>
+          <t>1→3·8d</t>
         </is>
       </c>
       <c r="Z407" s="2" t="inlineStr"/>
@@ -61976,7 +61960,7 @@
       </c>
       <c r="Y412" s="2" t="inlineStr">
         <is>
-          <t>1A→1·2d ← 1→1A·3d ← 3→1·18d</t>
+          <t>3→1·18d</t>
         </is>
       </c>
       <c r="Z412" s="2" t="inlineStr"/>
@@ -62271,12 +62255,12 @@
       </c>
       <c r="X414" s="2" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y414" s="2" t="inlineStr">
         <is>
-          <t>1B→1A·1d ← 1A→1B·2d ← 4→1A·3d</t>
+          <t>1+→1·1d ← 1→1+·2d ← 4→1·3d</t>
         </is>
       </c>
       <c r="Z414" s="2" t="inlineStr"/>
@@ -67056,7 +67040,7 @@
       </c>
       <c r="Y446" s="2" t="inlineStr">
         <is>
-          <t>3→2A·8d ← 1A→3·11d ← 3→1A·14d</t>
+          <t>3→2A·8d ← 1→3·11d ← 3→1·14d</t>
         </is>
       </c>
       <c r="Z446" s="2" t="inlineStr"/>
@@ -69260,14 +69244,10 @@
       </c>
       <c r="X461" s="2" t="inlineStr">
         <is>
-          <t>1A</t>
-        </is>
-      </c>
-      <c r="Y461" s="2" t="inlineStr">
-        <is>
-          <t>1→1A·5d ← 1A→1·10d ← 1→1A·12d</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y461" s="2" t="inlineStr"/>
       <c r="Z461" s="2" t="inlineStr"/>
       <c r="AA461" s="2" t="inlineStr"/>
       <c r="AB461" s="2" t="inlineStr">
@@ -69701,12 +69681,12 @@
       </c>
       <c r="X464" s="2" t="inlineStr">
         <is>
-          <t>1B(预金叉·纠缠)</t>
+          <t>1+(预金叉·纠缠)</t>
         </is>
       </c>
       <c r="Y464" s="2" t="inlineStr">
         <is>
-          <t>4→1B·3d ← 1→4·9d</t>
+          <t>4→1+·3d ← 1→4·9d</t>
         </is>
       </c>
       <c r="Z464" s="2" t="inlineStr"/>
@@ -70838,7 +70818,7 @@
       </c>
       <c r="Y472" s="2" t="inlineStr">
         <is>
-          <t>1A→1·5d ← 2A→1A·11d ← 1A→2A·14d</t>
+          <t>2A→1·11d ← 1→2A·14d</t>
         </is>
       </c>
       <c r="Z472" s="2" t="inlineStr"/>
@@ -71718,7 +71698,7 @@
       </c>
       <c r="Y478" s="2" t="inlineStr">
         <is>
-          <t>1A→3·6d ← 1B→1A·10d ← 1A→1B·11d</t>
+          <t>1→3·6d ← 1+→1·10d ← 1→1+·11d</t>
         </is>
       </c>
       <c r="Z478" s="2" t="inlineStr"/>
@@ -71865,7 +71845,7 @@
       </c>
       <c r="Y479" s="2" t="inlineStr">
         <is>
-          <t>1A→1·2d ← 4→1A·4d ← 4+→4·5d</t>
+          <t>4→1·4d ← 4+→4·5d ← 4→4+·6d</t>
         </is>
       </c>
       <c r="Z479" s="2" t="inlineStr"/>
@@ -73281,7 +73261,7 @@
       </c>
       <c r="Y489" s="2" t="inlineStr">
         <is>
-          <t>1A→1·2d ← 1B→1A·7d ← 1A→1B·8d</t>
+          <t>1+→1·7d ← 1→1+·8d ← 1+→1·9d</t>
         </is>
       </c>
       <c r="Z489" s="2" t="inlineStr"/>
@@ -73428,7 +73408,7 @@
       </c>
       <c r="Y490" s="2" t="inlineStr">
         <is>
-          <t>1A→3·5d ← 1→1A·6d</t>
+          <t>1→3·5d</t>
         </is>
       </c>
       <c r="Z490" s="2" t="inlineStr"/>
@@ -74436,12 +74416,12 @@
       </c>
       <c r="X497" s="2" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y497" s="2" t="inlineStr">
         <is>
-          <t>4→1A·9d</t>
+          <t>4→1·9d</t>
         </is>
       </c>
       <c r="Z497" s="2" t="inlineStr"/>
@@ -75654,7 +75634,7 @@
       </c>
       <c r="Y506" s="2" t="inlineStr">
         <is>
-          <t>1A→2A·7d</t>
+          <t>1→2A·7d</t>
         </is>
       </c>
       <c r="Z506" s="2" t="inlineStr">
@@ -77167,11 +77147,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y517" s="2" t="inlineStr">
-        <is>
-          <t>1A→1·4d ← 1→1A·5d</t>
-        </is>
-      </c>
+      <c r="Y517" s="2" t="inlineStr"/>
       <c r="Z517" s="2" t="inlineStr"/>
       <c r="AA517" s="2" t="inlineStr"/>
       <c r="AB517" s="2" t="inlineStr"/>
@@ -77844,7 +77820,7 @@
       </c>
       <c r="Y522" s="2" t="inlineStr">
         <is>
-          <t>1→4·5d ← 1A→1·6d ← 1→1A·7d</t>
+          <t>1→4·5d</t>
         </is>
       </c>
       <c r="Z522" s="2" t="inlineStr"/>
@@ -78798,12 +78774,12 @@
       </c>
       <c r="X529" s="2" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y529" s="2" t="inlineStr">
         <is>
-          <t>4→1A·6d ← 4+→4·13d ← 4→4+·16d</t>
+          <t>4→1·6d ← 4+→4·13d ← 4→4+·16d</t>
         </is>
       </c>
       <c r="Z529" s="2" t="inlineStr"/>
@@ -79059,7 +79035,7 @@
       </c>
       <c r="Y531" s="2" t="inlineStr">
         <is>
-          <t>1B→3·1d ← 4→1B·4d</t>
+          <t>1+→3·1d ← 4→1+·4d</t>
         </is>
       </c>
       <c r="Z531" s="2" t="inlineStr"/>
@@ -80955,7 +80931,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  子档(v2.1): 4+=止跌(日线MA5/10/20纠缠+快线&gt;慢线+周J超卖或底背离, 价&lt;EMA10W) | 1=过渡(价&lt;EMA10W) | 1A=早期修复(价≥EMA10W) | 1B=强筑底(站稳MA5/10/20全三条+全部斜率上行+周MACD DIF&gt;DEA; 标记:预金叉·纠缠·底背离) | 2A=修复态或刚确立(≤10日) | 2B=满配(slope10&gt;0·EMA10W&gt;EMA30W·10日前也是) | 2C=满配+延伸/减速/顶背离 | 3/4不分档。4+的标记: 周J超卖·底背离·日线纠缠; 2C的标记: 延伸(&gt;25%)·减速·顶背离</t>
+          <t xml:space="preserve">  子档(v2.1): 4+=止跌(日线MA5/10/20纠缠+快线&gt;慢线+周J超卖或底背离, 价&lt;EMA10W) | 1=筑底(不区分价格vs EMA10W) | 1+=强筑底(站稳MA5/10/20全三条+全上行+周MACD DIF&gt;DEA; 标记:预金叉·纠缠·底背离) | 2A=修复态或刚确立(≤10日) | 2B=满配(slope10&gt;0·EMA10W&gt;EMA30W·10日前也是) | 2C=满配+延伸/减速/顶背离 | 3/4不分档。4+的标记: 周J超卖·底背离·日线纠缠; 2C的标记: 延伸(&gt;25%)·减速·顶背离</t>
         </is>
       </c>
     </row>
